--- a/liaisons_Super_Constellation/Reseau_Pan_Am_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_Pan_Am_L1049_sourced.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Lignes Atlantique &amp; LatAm" sheetId="1" r:id="rId1"/>
-    <sheet name="Réseau Inter-Allemagne (IGS)" sheetId="2" r:id="rId2"/>
+    <sheet name="Lignes DC-6" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:I14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>N° Vol</v>
       </c>
       <c r="B1" t="str">
-        <v>Type de Ligne / Nom</v>
+        <v>Axe / Ligne</v>
       </c>
       <c r="C1" t="str">
         <v>Origine</v>
@@ -420,16 +419,13 @@
         <v>Escale 2 (Arr. / Dép.)</v>
       </c>
       <c r="G1" t="str">
-        <v>Escale 3 (Arr. / Dép.)</v>
+        <v>Destination</v>
       </c>
       <c r="H1" t="str">
-        <v>Destination</v>
+        <v>Arrivée (HL)</v>
       </c>
       <c r="I1" t="str">
-        <v>Arrivée (HL)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Fréquence / Notes</v>
+        <v>Fréquence / Note</v>
       </c>
     </row>
     <row r="2">
@@ -437,7 +433,7 @@
         <v>PA 100</v>
       </c>
       <c r="B2" t="str">
-        <v>Transatlantique</v>
+        <v>Atlantique Nord (Londres)</v>
       </c>
       <c r="C2" t="str">
         <v>New York (IDL)</v>
@@ -446,22 +442,19 @@
         <v>19:00</v>
       </c>
       <c r="E2" t="str">
-        <v>Gander [Tech] (00:30 / 01:45 *)</v>
+        <v>Gander [Tech] (00:00 * / 01:15 *)</v>
       </c>
       <c r="F2" t="str">
-        <v>Shannon (11:15 / 12:15 *)</v>
+        <v>Shannon (06:15 * / 07:15 *)</v>
       </c>
       <c r="G2" t="str">
-        <v>-</v>
+        <v>Londres (LHR)</v>
       </c>
       <c r="H2" t="str">
-        <v>Londres (LHR)</v>
+        <v>09:15 *</v>
       </c>
       <c r="I2" t="str">
-        <v>14:00 *</v>
-      </c>
-      <c r="J2" t="str">
-        <v>3x par semaine</v>
+        <v>Mardi, Jeudi, Samedi</v>
       </c>
     </row>
     <row r="3">
@@ -469,159 +462,144 @@
         <v>PA 101</v>
       </c>
       <c r="B3" t="str">
-        <v>Transatlantique (Retour)</v>
+        <v>Atlantique Nord (Retour)</v>
       </c>
       <c r="C3" t="str">
         <v>Londres (LHR)</v>
       </c>
       <c r="D3" t="str">
-        <v>16:00</v>
+        <v>12:00</v>
       </c>
       <c r="E3" t="str">
-        <v>Shannon (17:45 / 18:45)</v>
+        <v>Shannon (14:00 / 15:00)</v>
       </c>
       <c r="F3" t="str">
-        <v>Gander [Tech] (04:15 * / 05:30 *)</v>
+        <v>Gander [Tech] (20:00 / 21:15)</v>
       </c>
       <c r="G3" t="str">
-        <v>-</v>
+        <v>New York (IDL)</v>
       </c>
       <c r="H3" t="str">
-        <v>New York (IDL)</v>
+        <v>02:15 *</v>
       </c>
       <c r="I3" t="str">
-        <v>11:00 *</v>
-      </c>
-      <c r="J3" t="str">
-        <v>3x par semaine</v>
+        <v>Mercredi, Vendredi, Dimanche</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PA 151</v>
+        <v>PA 400</v>
       </c>
       <c r="B4" t="str">
-        <v>Amérique Latine</v>
+        <v>Caraïbes (San Juan)</v>
       </c>
       <c r="C4" t="str">
-        <v>Miami (MIA)</v>
+        <v>New York (IDL)</v>
       </c>
       <c r="D4" t="str">
-        <v>08:30</v>
+        <v>10:00</v>
       </c>
       <c r="E4" t="str">
-        <v>La Havane (09:30 / 10:00)</v>
+        <v>Bermudes (13:00 / 14:00)</v>
       </c>
       <c r="F4" t="str">
-        <v>Kingston (KIN) (12:15 / 13:00)</v>
+        <v>-</v>
       </c>
       <c r="G4" t="str">
-        <v>-</v>
+        <v>San Juan</v>
       </c>
       <c r="H4" t="str">
-        <v>Bogota (BOG)</v>
+        <v>19:00</v>
       </c>
       <c r="I4" t="str">
-        <v>16:30</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Quotidien</v>
+        <v>Mercredi, Samedi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>PA 152</v>
+        <v>PA 401</v>
       </c>
       <c r="B5" t="str">
-        <v>Amérique Latine (Retour)</v>
+        <v>Caraïbes (San Juan) (Retour)</v>
       </c>
       <c r="C5" t="str">
-        <v>Bogota (BOG)</v>
+        <v>San Juan</v>
       </c>
       <c r="D5" t="str">
-        <v>11:00</v>
+        <v>16:00</v>
       </c>
       <c r="E5" t="str">
-        <v>Kingston (KIN) (14:30 / 15:15)</v>
+        <v>Bermudes (21:00 / 22:00)</v>
       </c>
       <c r="F5" t="str">
-        <v>La Havane (17:30 / 18:00)</v>
+        <v>-</v>
       </c>
       <c r="G5" t="str">
-        <v>-</v>
+        <v>New York (IDL)</v>
       </c>
       <c r="H5" t="str">
-        <v>Miami (MIA)</v>
+        <v>01:00 *</v>
       </c>
       <c r="I5" t="str">
-        <v>19:00</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Quotidien</v>
+        <v>Lundi, Jeudi</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>PA 202</v>
+        <v>PA 500</v>
       </c>
       <c r="B6" t="str">
-        <v>Caraïbes / Amérique du Sud</v>
+        <v>Amérique Latine (Panama)</v>
       </c>
       <c r="C6" t="str">
-        <v>New York (IDL)</v>
+        <v>Miami</v>
       </c>
       <c r="D6" t="str">
-        <v>11:00</v>
+        <v>08:00</v>
       </c>
       <c r="E6" t="str">
-        <v>San Juan (SJU) (16:15 / 17:15)</v>
+        <v>La Havane (09:30 / 10:15)</v>
       </c>
       <c r="F6" t="str">
-        <v>Port of Spain (POS) (21:00 / 21:45)</v>
+        <v>-</v>
       </c>
       <c r="G6" t="str">
-        <v>-</v>
+        <v>Panama</v>
       </c>
       <c r="H6" t="str">
-        <v>Georgetown (GEO)</v>
+        <v>13:15</v>
       </c>
       <c r="I6" t="str">
-        <v>23:59</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2x par semaine</v>
+        <v>Mardi, Vendredi</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>PA 203</v>
+        <v>PA 501</v>
       </c>
       <c r="B7" t="str">
-        <v>Caraïbes / Amérique du Sud (Retour)</v>
+        <v>Amérique Latine (Retour)</v>
       </c>
       <c r="C7" t="str">
-        <v>Georgetown (GEO)</v>
+        <v>Panama</v>
       </c>
       <c r="D7" t="str">
-        <v>16:00</v>
+        <v>15:00</v>
       </c>
       <c r="E7" t="str">
-        <v>Port of Spain (POS) (18:14 / 18:59)</v>
+        <v>La Havane (18:00 / 18:45)</v>
       </c>
       <c r="F7" t="str">
-        <v>San Juan (SJU) (22:44 / 23:44)</v>
+        <v>-</v>
       </c>
       <c r="G7" t="str">
-        <v>-</v>
+        <v>Miami</v>
       </c>
       <c r="H7" t="str">
-        <v>New York (IDL)</v>
+        <v>20:15</v>
       </c>
       <c r="I7" t="str">
-        <v>04:59 *</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2x par semaine</v>
+        <v>Jeudi, Dimanche</v>
       </c>
     </row>
     <row r="8">
@@ -650,9 +628,6 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
         <v/>
       </c>
     </row>
@@ -684,13 +659,10 @@
       <c r="I9" t="str">
         <v/>
       </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ATTENTION : Pan Am n'a PAS exploité le Lockheed L-1049 Super Constellation. Elle utilisait le L-749 Constellation (dès 1946) puis le Boeing 377 Stratocruiser et les Douglas DC-6B / DC-7C. Les vols ci-dessous sont donc ENTIÈREMENT RECONSTITUÉS [R] et ne correspondent pas à une exploitation réelle du L-1049 par Pan Am.</v>
+        <v>Sources : Pan American a exploité de nombreux Douglas DC-6B (« President » Special) sur l'Atlantique Nord, les Caraïbes et l'Amérique latine.</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -714,15 +686,12 @@
         <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>[S] Sourcé : seulement les corridors réels du réseau Pan Am (Atlantique Nord, Amérique latine) — pas l'appareil.</v>
+        <v>Ligne exploitée historiquement en Douglas DC-6 ; proposée ici pour le Super Constellation L-1049, appareil de même catégorie (quadrimoteur à pistons long-courrier).</v>
       </c>
       <c r="B11" t="str">
         <v/>
@@ -746,15 +715,12 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>[R] Reconstitué : la totalité de l'exploitation en L-1049 (fictive), numéros et horaires.</v>
+        <v>[R] Reconstitué : numéros de vol et horaires — non issus d'un timetable original.</v>
       </c>
       <c r="B12" t="str">
         <v/>
@@ -778,15 +744,12 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>* Arrivée le lendemain (+1 jour). HL : Heure Locale.</v>
+        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
       </c>
       <c r="B13" t="str">
         <v/>
@@ -810,322 +773,41 @@
         <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>[R] Vols retour ajoutés automatiquement (itinéraire miroir, horaires reconstitués).</v>
+        <v>[R] Vols retour reconstitués par itinéraire miroir (horaires plausibles).</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>N° Vol</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Secteur</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Origine</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Départ (HL)</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Escale 1 (Arr. / Dép.)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Destination</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Arrivée (HL)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Notes / Contexte Historique</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PA 602</v>
-      </c>
-      <c r="B2" t="str">
-        <v>IGS Corridor Nord</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Berlin (THF)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>07:30</v>
-      </c>
-      <c r="E2" t="str">
-        <v>-</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Hambourg (HAM)</v>
-      </c>
-      <c r="G2" t="str">
-        <v>08:30</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Navette quotidienne</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>PA 603</v>
-      </c>
-      <c r="B3" t="str">
-        <v>IGS Corridor Nord (Retour)</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Hambourg (HAM)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="E3" t="str">
-        <v>-</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Berlin (THF)</v>
-      </c>
-      <c r="G3" t="str">
-        <v>10:00</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Navette quotidienne</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PA 614</v>
-      </c>
-      <c r="B4" t="str">
-        <v>IGS Corridor Centre</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Berlin (THF)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>11:00</v>
-      </c>
-      <c r="E4" t="str">
-        <v>-</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Francfort (FRA)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>12:15</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Connexion transatlantique</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PA 615</v>
-      </c>
-      <c r="B5" t="str">
-        <v>IGS Corridor Centre (Retour)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Francfort (FRA)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="E5" t="str">
-        <v>-</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Berlin (THF)</v>
-      </c>
-      <c r="G5" t="str">
-        <v>10:15</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Connexion transatlantique</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>PA 620</v>
-      </c>
-      <c r="B6" t="str">
-        <v>IGS Corridor Sud</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Berlin (THF)</v>
-      </c>
-      <c r="D6" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="E6" t="str">
-        <v>-</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Munich (MUC)</v>
-      </c>
-      <c r="G6" t="str">
-        <v>17:20</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Contournement du blocus terrestre</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>PA 621</v>
-      </c>
-      <c r="B7" t="str">
-        <v>IGS Corridor Sud (Retour)</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Munich (MUC)</v>
-      </c>
-      <c r="D7" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="E7" t="str">
-        <v>-</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Berlin (THF)</v>
-      </c>
-      <c r="G7" t="str">
-        <v>10:20</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Contournement du blocus terrestre</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Contexte Historique IGS :</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Le réseau IGS de Berlin était réel (seules Pan Am, BEA et Air France pouvaient desservir Berlin-Tempelhof), mais il était assuré en DC-4 puis DC-6B — PAS en L-1049. Feuillet fourni pour parité avec l'appli ; données [R] reconstituées.</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>HL : Heure Locale.</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>[R] Vols retour ajoutés automatiquement (itinéraire miroir, horaires reconstitués).</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
   </ignoredErrors>
 </worksheet>
 </file>